--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484030_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484030_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8155</v>
+        <v>1.3357</v>
       </c>
       <c r="E2" t="n">
-        <v>4.41</v>
+        <v>4.1265</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5944</v>
+        <v>-2.7908</v>
       </c>
       <c r="G2" t="n">
         <v>-1.594</v>
@@ -610,13 +610,13 @@
         <v>0.5952</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1423</v>
+        <v>-0.6221</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1191</v>
+        <v>-0.1643</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2614</v>
+        <v>-0.4577</v>
       </c>
       <c r="V2" t="n">
         <v>3.3534</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.0659</v>
+        <v>-2.6601</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5683</v>
+        <v>-2.0434</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.6342</v>
+        <v>-0.6167</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.7361</v>
+        <v>-1.8931</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8188</v>
+        <v>-1.7791</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9173</v>
+        <v>-0.114</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3309</v>
+        <v>0.0429</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1301</v>
+        <v>-0.6399</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2008</v>
+        <v>0.6827</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.067</v>
+        <v>-1.936</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.9489</v>
+        <v>-1.1392</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1181</v>
+        <v>-0.7967</v>
       </c>
       <c r="P3" t="n">
         <v>-0.7935</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.579</v>
+        <v>-2.1822</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2573</v>
+        <v>-0.2395</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6099</v>
+        <v>-0.17</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3526</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.4596</v>
+        <v>-2.7073</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2135</v>
+        <v>-0.2929</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2461</v>
+        <v>-2.4145</v>
       </c>
       <c r="G4" t="n">
         <v>-1.8669</v>
@@ -766,13 +766,13 @@
         <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3106</v>
+        <v>-0.5583</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0056</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.305</v>
+        <v>-0.4733</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4724</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.1354</v>
+        <v>-2.9717</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4345</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7009</v>
+        <v>-3.7464</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8931</v>
+        <v>-3.7361</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7791</v>
+        <v>-1.8188</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.114</v>
+        <v>-1.9173</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0429</v>
+        <v>1.3309</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6399</v>
+        <v>1.1301</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6827</v>
+        <v>0.2008</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.936</v>
+        <v>-5.067</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1392</v>
+        <v>-2.9489</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7967</v>
+        <v>-2.1181</v>
       </c>
       <c r="P5" t="n">
         <v>-0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1822</v>
+        <v>-2.579</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7147</v>
+        <v>0.3515</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5611</v>
+        <v>0.8163</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1536</v>
+        <v>-0.4649</v>
       </c>
       <c r="V5" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>M. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.6237</v>
+        <v>-3.3971</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8085</v>
+        <v>1.1084</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8152</v>
+        <v>-4.5055</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9485</v>
+        <v>-2.153</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9807</v>
+        <v>-2.2825</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9678</v>
+        <v>0.1295</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6749000000000001</v>
+        <v>3.2452</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6399</v>
+        <v>0.868</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0351</v>
+        <v>2.3772</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2736</v>
+        <v>-5.3982</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3408</v>
+        <v>-3.1505</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9328</v>
+        <v>-2.2477</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1903</v>
+        <v>-2.3806</v>
       </c>
       <c r="R6" t="n">
         <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2703</v>
+        <v>-0.2522</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0567</v>
+        <v>0.2439</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3271</v>
+        <v>-0.496</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.8941</v>
+        <v>-3.429</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5532</v>
+        <v>-0.0601</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.3409</v>
+        <v>-3.3689</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0677</v>
@@ -1000,13 +1000,13 @@
         <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2827</v>
+        <v>-0.8176</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8105</v>
+        <v>-0.3174</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4722</v>
+        <v>-0.5003</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9405</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9928</v>
+        <v>-3.573</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9172</v>
+        <v>-1.7858</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0755</v>
+        <v>-1.7872</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.5868</v>
+        <v>-2.9485</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8012</v>
+        <v>-1.9807</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.7856</v>
+        <v>-0.9678</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6623</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9379999999999999</v>
+        <v>-0.6399</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.6003</v>
+        <v>-0.0351</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9245</v>
+        <v>-2.2736</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7392</v>
+        <v>-1.3408</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1853</v>
+        <v>-0.9328</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1995</v>
+        <v>-0.2196</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0566</v>
+        <v>0.0794</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1429</v>
+        <v>-0.299</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GARCIA CALVO</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1277</v>
+        <v>-3.6969</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4339</v>
+        <v>-1.5091</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.5616</v>
+        <v>-2.1877</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.153</v>
+        <v>-4.5868</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2825</v>
+        <v>-0.8012</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1295</v>
+        <v>-3.7856</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2452</v>
+        <v>-1.6623</v>
       </c>
       <c r="K9" t="n">
-        <v>0.868</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3772</v>
+        <v>-2.6003</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.3982</v>
+        <v>-2.9245</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.1505</v>
+        <v>-1.7392</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2477</v>
+        <v>-1.1853</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3806</v>
+        <v>-0.1984</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9828</v>
+        <v>0.0964</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4307</v>
+        <v>0.3515</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5521</v>
+        <v>-0.2551</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3666</v>
+        <v>-3.8299</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3758</v>
+        <v>-0.0074</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9908</v>
+        <v>-3.8225</v>
       </c>
       <c r="G10" t="n">
         <v>-4.7222</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3785</v>
+        <v>-0.8417</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1813</v>
+        <v>0.1871</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1972</v>
+        <v>-1.0288</v>
       </c>
       <c r="V10" t="n">
         <v>0.9405</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8714</v>
+        <v>-5.8042</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5769</v>
+        <v>-5.5939</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2944</v>
+        <v>-0.2103</v>
       </c>
       <c r="G11" t="n">
         <v>-3.989</v>
@@ -1312,13 +1312,13 @@
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0969</v>
+        <v>-0.0297</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0567</v>
+        <v>0.0397</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1536</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4648</v>
+        <v>-6.2724</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1245</v>
+        <v>-2.9601</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3403</v>
+        <v>-3.3123</v>
       </c>
       <c r="G12" t="n">
         <v>-1.237</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3667</v>
+        <v>-0.1743</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2494</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6789</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6816</v>
+        <v>-6.6153</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3551</v>
+        <v>-2.4571</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.3265</v>
+        <v>-4.1582</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5866</v>
@@ -1468,13 +1468,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4999</v>
+        <v>-0.4336</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6236</v>
+        <v>0.5216</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1235</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6032</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-44.8681</v>
+        <v>-43.62119999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.947</v>
+        <v>-10.7002</v>
       </c>
       <c r="F14" t="n">
-        <v>-32.9208</v>
+        <v>-32.921</v>
       </c>
       <c r="G14" t="n">
         <v>-35.3809</v>
@@ -1531,7 +1531,7 @@
         <v>-33.9497</v>
       </c>
       <c r="N14" t="n">
-        <v>-20.76840000000001</v>
+        <v>-20.7684</v>
       </c>
       <c r="O14" t="n">
         <v>-13.1813</v>
@@ -1546,16 +1546,16 @@
         <v>13.8869</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.9876</v>
+        <v>-3.7407</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1708000000000001</v>
+        <v>1.4178</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.1585</v>
+        <v>-5.158499999999998</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5317999999999998</v>
+        <v>-0.5317999999999994</v>
       </c>
       <c r="W14" t="n">
         <v>7.1676</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1378</v>
+        <v>7.6216</v>
       </c>
       <c r="E15" t="n">
         <v>2.0395</v>
       </c>
       <c r="F15" t="n">
-        <v>5.0984</v>
+        <v>5.5822</v>
       </c>
       <c r="G15" t="n">
         <v>3.8919</v>
@@ -1624,13 +1624,13 @@
         <v>2.7774</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1864</v>
+        <v>0.6702</v>
       </c>
       <c r="T15" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1183</v>
+        <v>0.6021</v>
       </c>
       <c r="V15" t="n">
         <v>1.4724</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8929</v>
+        <v>6.4953</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4752</v>
+        <v>3.5674</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4176</v>
+        <v>2.9279</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8874</v>
+        <v>4.6688</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9262</v>
+        <v>0.4026</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0388</v>
+        <v>4.2662</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2961</v>
+        <v>3.607</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0953</v>
+        <v>-0.0955</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2008</v>
+        <v>3.7025</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5913</v>
+        <v>1.0618</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8309</v>
+        <v>0.4981</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2396</v>
+        <v>0.5637</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0054</v>
+        <v>0.6362</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3694</v>
+        <v>-0.0396</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.364</v>
+        <v>0.6758</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5013</v>
+        <v>6.4894</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0573</v>
+        <v>5.3985</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4441</v>
+        <v>1.0909</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6688</v>
+        <v>5.4805</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4026</v>
+        <v>2.3284</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2662</v>
+        <v>3.1521</v>
       </c>
       <c r="J17" t="n">
-        <v>3.607</v>
+        <v>4.0171</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0955</v>
+        <v>1.9663</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7025</v>
+        <v>2.0508</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0618</v>
+        <v>1.4634</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4981</v>
+        <v>0.3621</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5637</v>
+        <v>1.1013</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3578</v>
+        <v>0.017</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5498</v>
+        <v>-0.0396</v>
       </c>
       <c r="U17" t="n">
-        <v>0.192</v>
+        <v>0.0566</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. PARADEDA VIDAL</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.2988</v>
+        <v>5.483</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9845</v>
+        <v>3.3529</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3143</v>
+        <v>2.1301</v>
       </c>
       <c r="G18" t="n">
-        <v>5.9965</v>
+        <v>3.8874</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2861</v>
+        <v>3.9262</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7103</v>
+        <v>-0.0388</v>
       </c>
       <c r="J18" t="n">
-        <v>6.5672</v>
+        <v>3.2961</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8763</v>
+        <v>3.0953</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6908</v>
+        <v>0.2008</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5707</v>
+        <v>0.5913</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.8309</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0195</v>
+        <v>-0.2396</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.579</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.9596</v>
+        <v>-1.1903</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3806</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6154</v>
+        <v>1.5956</v>
       </c>
       <c r="T18" t="n">
-        <v>1.111</v>
+        <v>1.2471</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5044</v>
+        <v>0.3485</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.9516</v>
+        <v>5.46</v>
       </c>
       <c r="E19" t="n">
-        <v>5.6781</v>
+        <v>5.8821</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7265</v>
+        <v>-0.4221</v>
       </c>
       <c r="G19" t="n">
         <v>4.8555</v>
@@ -1936,13 +1936,13 @@
         <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7074</v>
+        <v>1.2158</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.7086</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2029</v>
+        <v>0.5072</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2065</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.8501</v>
+        <v>5.4537</v>
       </c>
       <c r="E20" t="n">
-        <v>4.8883</v>
+        <v>2.8226</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0382</v>
+        <v>2.6311</v>
       </c>
       <c r="G20" t="n">
-        <v>5.4805</v>
+        <v>3.2389</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3284</v>
+        <v>2.7972</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1521</v>
+        <v>0.4418</v>
       </c>
       <c r="J20" t="n">
-        <v>4.0171</v>
+        <v>3.259</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9663</v>
+        <v>2.5711</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0508</v>
+        <v>0.6879</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4634</v>
+        <v>-0.02</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3621</v>
+        <v>0.226</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1013</v>
+        <v>-0.2461</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6222</v>
+        <v>1.0245</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5498</v>
+        <v>0.5555</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0725</v>
+        <v>0.469</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>E. PARADEDA VIDAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4.8118</v>
+        <v>4.9843</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7206</v>
+        <v>2.6784</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0912</v>
+        <v>2.3058</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2389</v>
+        <v>5.9965</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7972</v>
+        <v>3.2861</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4418</v>
+        <v>2.7103</v>
       </c>
       <c r="J21" t="n">
-        <v>3.259</v>
+        <v>6.5672</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5711</v>
+        <v>3.8763</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6879</v>
+        <v>2.6908</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.02</v>
+        <v>-0.5707</v>
       </c>
       <c r="N21" t="n">
-        <v>0.226</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2461</v>
+        <v>0.0195</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1903</v>
+        <v>-2.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-4.9596</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3825</v>
+        <v>1.3008</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4535</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.4959</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.6803</v>
+        <v>3.4444</v>
       </c>
       <c r="E22" t="n">
-        <v>4.6935</v>
+        <v>1.3799</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0133</v>
+        <v>2.0645</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5738</v>
+        <v>1.3396</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7566</v>
+        <v>0.7708</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1828</v>
+        <v>0.5688</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5445</v>
+        <v>1.1087</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9436</v>
+        <v>0.4234</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3991</v>
+        <v>0.6853</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9707</v>
+        <v>0.2309</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.187</v>
+        <v>0.3474</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7837</v>
+        <v>-0.1165</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3968</v>
+        <v>0.3968</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2372</v>
+        <v>0.5016</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9896</v>
+        <v>0.2551</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2476</v>
+        <v>0.2465</v>
       </c>
       <c r="V22" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3417</v>
+        <v>1.2065</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.0584</v>
+        <v>2.972</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0739</v>
+        <v>3.8773</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9845</v>
+        <v>-0.9053</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3396</v>
+        <v>1.5738</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7708</v>
+        <v>2.7566</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5688</v>
+        <v>-1.1828</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1087</v>
+        <v>2.5445</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4234</v>
+        <v>2.9436</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6853</v>
+        <v>-0.3991</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2309</v>
+        <v>-0.9707</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3474</v>
+        <v>-0.187</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1165</v>
+        <v>-0.7837</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1156</v>
+        <v>1.529</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.051</v>
+        <v>1.1734</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1666</v>
+        <v>0.3556</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2065</v>
+        <v>2.3417</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3149</v>
+        <v>0.5455</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3102</v>
+        <v>1.9223</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6251</v>
+        <v>-1.3768</v>
       </c>
       <c r="G24" t="n">
         <v>0.4479</v>
@@ -2326,13 +2326,13 @@
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2823</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.187</v>
+        <v>0.4251</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0953</v>
+        <v>0.153</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4724</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>44.8681</v>
+        <v>48.9492</v>
       </c>
       <c r="E25" t="n">
-        <v>32.9211</v>
+        <v>32.9209</v>
       </c>
       <c r="F25" t="n">
-        <v>11.947</v>
+        <v>16.0283</v>
       </c>
       <c r="G25" t="n">
-        <v>35.38079999999999</v>
+        <v>35.3808</v>
       </c>
       <c r="H25" t="n">
         <v>21.972</v>
@@ -2392,7 +2392,7 @@
         <v>1.2033</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2274999999999998</v>
+        <v>0.2274999999999999</v>
       </c>
       <c r="P25" t="n">
         <v>3.9677</v>
@@ -2404,13 +2404,13 @@
         <v>17.8546</v>
       </c>
       <c r="S25" t="n">
-        <v>4.987599999999999</v>
+        <v>9.0688</v>
       </c>
       <c r="T25" t="n">
-        <v>5.158499999999999</v>
+        <v>5.1586</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1710000000000001</v>
+        <v>3.9102</v>
       </c>
       <c r="V25" t="n">
         <v>0.532</v>
